--- a/Talent360i_Output.xlsx
+++ b/Talent360i_Output.xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1443,131 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>2026-09-11T12:02:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ASG-20260917135151435635</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Q-0043</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Skip documentation to meet speed targets and update records after the close cycle.</t>
+        </is>
+      </c>
+      <c r="D17" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:52:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ASG-20260917135151435635</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Q-0046</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Resolve the item informally without linking the action to controls, metrics or evidence.</t>
+        </is>
+      </c>
+      <c r="D18" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:52:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ASG-20260917135151435635</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Q-0047</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Apply the SOP, maintain evidence, escalate exceptions, and document the rationale for AP Reconciliations (Subledger/GL, Vendor Statements).</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:52:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ASG-20260917135151435635</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Q-0049</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Follow the standard SOP only when instructed and wait for review before taking action.</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:52:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ASG-20260917135151435635</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Q-0050</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Apply the SOP, maintain evidence, escalate exceptions, and document the rationale for Ownership &amp; Delivery.</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:52:48</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1725,6 +1850,72 @@
         </is>
       </c>
       <c r="N4" t="inlineStr">
+        <is>
+          <t>Application-calculated result awaiting calibration</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RST-20260917135248973504</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ASG-20260917135151435635</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SYN-U017</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SCH-005</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I5" t="n">
+        <v>75</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Application-calculated result awaiting calibration</t>
         </is>
@@ -1741,7 +1932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1987,6 +2178,64 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>RST-20260911120241582044</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>USA-20260917135315504185</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SYN-U017</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AP_invoice_processing_po_non_po</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Invoice Processing (PO &amp; Non-PO)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Invoice Processing (PO &amp; Non-PO)</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Assessed</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>RST-20260917135248973504</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2141,6 +2390,8 @@
           <t>Assign mapped microlearning / scenario lab and reassess</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2202,6 +2453,8 @@
           <t>Assign mapped microlearning / scenario lab and reassess</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2263,6 +2516,71 @@
           <t>Assign mapped microlearning / scenario lab and reassess</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GAP-20260917135316179340</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SYN-U017</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AP_invoice_processing_po_non_po</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Invoice Processing (PO &amp; Non-PO)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Invoice Processing (PO &amp; Non-PO)</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>TRN-0008</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Assign mapped microlearning / scenario lab and reassess</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2639,7 +2957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3046,6 +3364,51 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>2026-09-11T12:01:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>REQ-20260917135108456956</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SYN-U017</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>P2P Senior Associate</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Close Activities (Accruals, Cutoff, GR/IR)</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:51:08</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3393,6 +3756,43 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>2026-09-11T12:01:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AUD-20260917135108456956</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>assessment_request</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>REQ-20260917135108456956</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SYN-U017</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skill=Close Activities (Accruals, Cutoff, GR/IR), Level=2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:51:09</t>
         </is>
       </c>
     </row>
@@ -18639,7 +19039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19001,6 +19401,58 @@
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>Created from approved question bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ASG-20260917135151435635</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SYN-U017</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SCH-005</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Created from approved question bank</t>
         </is>
@@ -19017,7 +19469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19392,6 +19844,66 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ASG-20260917135151435635</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Q-0043</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ASG-20260917135151435635</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Q-0046</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ASG-20260917135151435635</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Q-0050</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ASG-20260917135151435635</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Q-0047</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ASG-20260917135151435635</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Q-0049</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Talent360i_Output.xlsx
+++ b/Talent360i_Output.xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1693,6 +1693,256 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>2026-09-18T12:43:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ASG-20260908181908557305</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Q-0086</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Apply the SOP, maintain evidence, escalate exceptions, and document the rationale for First Time Right (Quality, SOX/ICFR-ready).</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:18:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ASG-20260908181908557305</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Q-0088</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Apply the SOP, maintain evidence, escalate exceptions, and document the rationale for R2R Close &amp; Journals (US GAAP / IFRS).</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:18:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ASG-20260908181908557305</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Q-0090</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Follow the standard SOP only when instructed and wait for review before taking action.</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:18:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ASG-20260908181908557305</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Q-0093</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Skip documentation to meet speed targets and update records after the close cycle.</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:18:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ASG-20260908181908557305</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Q-0095</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Follow the standard SOP only when instructed and wait for review before taking action.</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:18:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ASG-20260918154126177293</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154018479929</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-09-18T15:42:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ASG-20260918154126177293</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154021852116</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Net income is understated</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-09-18T15:42:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ASG-20260918154126177293</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154022601290</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Duplicate invoices</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-09-18T15:42:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ASG-20260918154126177293</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154023364623</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>By January 15 of the following year</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-09-18T15:42:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ASG-20260918154126177293</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154024342195</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>When a goods receipt is recorded</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-09-18T15:42:24</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1796,6 +2046,11 @@
           <t>sme_signoff</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>manager_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2137,6 +2392,156 @@
       <c r="Q6" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RST-20260918131857776584</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ASG-20260908181908557305</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SYN-U001</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SCH-001</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" t="n">
+        <v>75</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Application-calculated result awaiting calibration</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RST-20260918154224606587</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ASG-20260918154126177293</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SYN-U015</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SCH-004</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>20</v>
+      </c>
+      <c r="I8" t="n">
+        <v>75</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Sent Back</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Application-calculated result awaiting calibration</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>you can do better</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2513,6 +2918,64 @@
       <c r="L6" t="inlineStr">
         <is>
           <t>RST-20260918124306873360</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>USA-20260918131930592573</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SYN-U001</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>R2R_first_time_right_quality_sox_icfr_ready</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>First Time Right (Quality, SOX/ICFR-ready)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>First Time Right (Quality, SOX/ICFR-ready)</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Assessed</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>RST-20260918131857776584</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2667,8 +3130,6 @@
           <t>Assign mapped microlearning / scenario lab and reassess</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2730,8 +3191,6 @@
           <t>Assign mapped microlearning / scenario lab and reassess</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2793,8 +3252,6 @@
           <t>Assign mapped microlearning / scenario lab and reassess</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2856,8 +3313,6 @@
           <t>Assign mapped microlearning / scenario lab and reassess</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2919,8 +3374,72 @@
           <t>No action - at target</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GAP-20260918131931362118</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SYN-U001</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>R2R_first_time_right_quality_sox_icfr_ready</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>First Time Right (Quality, SOX/ICFR-ready)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>First Time Right (Quality, SOX/ICFR-ready)</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>TRN-0035</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Assign mapped microlearning / scenario lab and reassess</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Consider adjacent skill exposure: Attention to Detail (SOX evidence trail / documentation), R2R Close &amp; Journals (US GAAP / IFRS), Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3297,7 +3816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3749,6 +4268,141 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>2026-09-17T13:51:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>REQ-20260918131643961965</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SYN-U001</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Banking Preparer Job (Preparation + Cash Posting)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Duplicate</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:16:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>REQ-20260918131647264116</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SYN-U001</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Banking Preparer Job (Preparation + Cash Posting)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REQ-20260918153927569338</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SYN-U015</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>P2P Lead</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Close Activities (Accruals, Cutoff, GR/IR)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-18T15:39:27</t>
         </is>
       </c>
     </row>
@@ -3763,7 +4417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4133,6 +4787,117 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>2026-09-17T13:51:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AUD-20260918131643961965</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>assessment_request</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>REQ-20260918131643961965</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SYN-U001</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skill=Reconciliations &amp; Clearing (SOX/IPE balance sheet recs), Level=3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:16:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AUD-20260918131647264116</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>assessment_request</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>REQ-20260918131647264116</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SYN-U001</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skill=Reconciliations &amp; Clearing (SOX/IPE balance sheet recs), Level=3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:16:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AUD-20260918153927569338</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>assessment_request</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>REQ-20260918153927569338</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SYN-U015</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skill=Close Activities (Accruals, Cutoff, GR/IR), Level=5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-09-18T15:39:28</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N168"/>
+  <dimension ref="A1:N191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14534,6 +15299,1501 @@
       <c r="N168" t="inlineStr">
         <is>
           <t>abcjf</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>REV-20260918131802766768</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131740629017</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>1</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>REV-20260918131803481580</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131742393593</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>REV-20260918131804203693</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131743443724</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Needs Regeneration</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Regenerate</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Regenerate question</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>REV-20260918131805154554</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131736996198</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>REV-20260918131805912066</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131738788487</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Needs Revision</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Rewrite required</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>REV-20260918131806736040</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131739821454</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>REV-20260918131807554495</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131736310443</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>REV-20260918131808549751</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131741654675</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>REV-20260918131809429615</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131737764356</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Needs Revision</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Rewrite required</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>REV-20260918131810212550</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131744526237</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>REV-20260918154042151163</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131743443724</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>REV-20260918154042870715</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131738788487</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>REV-20260918154043579265</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154021852116</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>REV-20260918154044508979</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154023364623</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>1</v>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>REV-20260918154045200330</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154025094672</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>1</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>REV-20260918154045969209</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154020167950</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>1</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>REV-20260918154046974353</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131737764356</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>1</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Rejected: not suitable</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>REV-20260918154047675207</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154019404834</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>1</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>REV-20260918154048420952</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154022601290</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>REV-20260918154049181269</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154017751590</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>REV-20260918154050151651</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154018479929</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>1</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>REV-20260918154050863599</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154024342195</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>1</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>REV-20260918154051584649</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154020877086</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -14548,7 +16808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA121"/>
+  <dimension ref="A1:AA141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29023,6 +31283,2406 @@
         </is>
       </c>
       <c r="X121" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131736310443</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>R2R</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Banking Preparer Job (Preparation + Cash Posting)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>3</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>What is the primary purpose of balance sheet reconciliations in the context of SOX compliance?</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>To identify discrepancies in financial reporting</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>To enhance cash flow management</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>To prepare for external audits</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>To improve operational efficiency</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>{"skill": "Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)", "level": 3}</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131736996198</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>R2R</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Banking Preparer Job (Preparation + Cash Posting)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>3</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Which of the following is a key component of an effective reconciliation process?</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Monthly financial statements</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Automated transaction recording</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Documentation of reconciliation procedures</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Frequent changes in accounting policies</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>{"skill": "Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)", "level": 3}</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131737764356</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>R2R</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Banking Preparer Job (Preparation + Cash Posting)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>3</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>When performing a reconciliation, which account is typically reconciled against bank statements?</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>{"skill": "Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)", "level": 3}</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131738788487</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>R2R</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Banking Preparer Job (Preparation + Cash Posting)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>3</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>In the context of IPE (Information Produced by the Entity), which of the following is true?</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>IPE is always external data.</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>IPE must be subject to controls and must be reliable.</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>IPE does not require documentation.</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>IPE is irrelevant to reconciliations.</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>{"skill": "Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)", "level": 3}</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131739821454</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>R2R</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Banking Preparer Job (Preparation + Cash Posting)</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>3</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>What is the minimum frequency for performing balance sheet reconciliations according to best practices?</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Annually</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>{"skill": "Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)", "level": 3}</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131740629017</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>R2R</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Banking Preparer Job (Preparation + Cash Posting)</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>3</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Which of the following is NOT a common reason for reconciling accounts?</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>To find errors in the accounting system</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>To comply with legal requirements</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>To prepare tax returns</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>To enhance employee engagement</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>{"skill": "Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)", "level": 3}</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131741654675</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>R2R</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Banking Preparer Job (Preparation + Cash Posting)</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>3</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>What is the role of variance analysis in the reconciliation process?</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>To determine the tax implications of transactions</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>To explain differences between actual and expected results</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>To finalize financial statements</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>To automate data entry in accounting systems</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>{"skill": "Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)", "level": 3}</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131742393593</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>R2R</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Banking Preparer Job (Preparation + Cash Posting)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>3</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Which document is commonly used to support the reconciliation of accounts?</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Trial balance</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Bank statement</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Income statement</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Cash flow statement</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>{"skill": "Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)", "level": 3}</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131743443724</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>R2R</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Banking Preparer Job (Preparation + Cash Posting)</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>3</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>What does SOX stand for, and what is its primary objective?</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Sarbanes-Oxley Act; to enhance corporate governance and accountability</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Securities and Options Exchange; to regulate stock transactions</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Standardized Operations for Exchanges; to streamline trading processes</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Sales and Operations Excellence; to improve business performance</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>{"skill": "Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)", "level": 3}</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131744526237</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>R2R</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Banking Preparer Job (Preparation + Cash Posting)</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>R2R_reconciliations_clearing_sox_ipe_balance_sheet_recs</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>3</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>How can technology aid in the reconciliation process?</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>By reducing the need for documentation</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>By enabling real-time data analysis and reporting</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>By eliminating the need for periodic audits</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>By standardizing all accounting practices across industries</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>{"skill": "Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)", "level": 3}</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154017751590</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>P2P Lead</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Close Activities (Accruals, Cutoff, GR/IR)</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>5</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>What does GR/IR stand for in accounting?</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Goods Receipt/Invoice Receipt</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Gross Revenue/Invoice Revenue</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Goods Revenue/Inventory Receipt</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>General Receipt/Inventory Receipt</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>{"skill": "Close Activities (Accruals, Cutoff, GR/IR)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154018479929</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>P2P Lead</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Close Activities (Accruals, Cutoff, GR/IR)</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>5</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Which of the following is typically accrued at the end of an accounting period?</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Cash sales</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Accounts receivable</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Utilities expense</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Inventory purchases</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>{"skill": "Close Activities (Accruals, Cutoff, GR/IR)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154019404834</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>P2P Lead</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Close Activities (Accruals, Cutoff, GR/IR)</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>5</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>In the context of cutoff procedures, which of the following actions is most critical?</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Recording all sales transactions</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Ensuring all inventory counts are accurate</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Confirming that expenses are recorded in the correct period</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Documenting customer complaints</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>{"skill": "Close Activities (Accruals, Cutoff, GR/IR)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154020167950</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>P2P Lead</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Close Activities (Accruals, Cutoff, GR/IR)</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>5</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>What is the primary purpose of accrual accounting?</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>To track cash flow</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>To match revenues with expenses</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>To simplify tax calculations</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>To increase profit margins</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>{"skill": "Close Activities (Accruals, Cutoff, GR/IR)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154020877086</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>P2P Lead</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Close Activities (Accruals, Cutoff, GR/IR)</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>5</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>When should you recognize accrued liabilities?</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>When cash is paid</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>When the obligation is created</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>When the invoice is received</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>At the end of the fiscal year only</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>{"skill": "Close Activities (Accruals, Cutoff, GR/IR)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154021852116</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>P2P Lead</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Close Activities (Accruals, Cutoff, GR/IR)</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>5</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>What is the effect of under-accruing liabilities on financial statements?</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Assets are overstated</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Liabilities are overstated</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Net income is understated</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Equity is unaffected</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>{"skill": "Close Activities (Accruals, Cutoff, GR/IR)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154022601290</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>P2P Lead</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Close Activities (Accruals, Cutoff, GR/IR)</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>5</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Which of the following is a common issue when performing GR/IR reconciliations?</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Excess inventory levels</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Duplicate invoices</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Inaccurate sales forecasts</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Delayed vendor payments</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>{"skill": "Close Activities (Accruals, Cutoff, GR/IR)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154023364623</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>P2P Lead</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Close Activities (Accruals, Cutoff, GR/IR)</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>5</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>In a business with a fiscal year ending December 31, when should a company accrue for services received in December but not yet billed?</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>By January 15 of the following year</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>At the end of December</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>When the bill is received</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>At the start of the next fiscal year</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>{"skill": "Close Activities (Accruals, Cutoff, GR/IR)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154024342195</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>P2P Lead</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Close Activities (Accruals, Cutoff, GR/IR)</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>5</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>In which situation would you most likely need to adjust the GR/IR account?</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>When inventory is sold</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>When a goods receipt is recorded</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>When an invoice is received after the period-end</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>When cash is received from customers</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>{"skill": "Close Activities (Accruals, Cutoff, GR/IR)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154025094672</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>P2P Lead</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>AP_close_activities_accruals_cutoff_gr_ir</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Close Activities (Accruals, Cutoff, GR/IR)</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>5</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Which financial statement is primarily affected by the accrual of unpaid expenses?</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Balance Sheet</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Cash Flow Statement</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>{"skill": "Close Activities (Accruals, Cutoff, GR/IR)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
         <is>
           <t>Requires SME approval before scheduling</t>
         </is>
@@ -29039,7 +33699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29241,7 +33901,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -29507,6 +34167,110 @@
       <c r="J9" t="inlineStr">
         <is>
           <t>Created from approved question bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ASG-20260918131835860727</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SYN-U001</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>R2R_banking_preparer_job_preparation_cash_posting</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>BP-001</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SCH-001</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Created from approved question bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ASG-20260918154126177293</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SYN-U015</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AP_p2p_lead</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>BP-004</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SCH-004</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>you can do better</t>
         </is>
       </c>
     </row>
@@ -29521,7 +34285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30016,6 +34780,126 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ASG-20260918131835860727</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131736996198</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ASG-20260918131835860727</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131742393593</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ASG-20260918131835860727</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131740629017</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ASG-20260918131835860727</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131739821454</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ASG-20260918131835860727</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918131744526237</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ASG-20260918154126177293</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154018479929</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ASG-20260918154126177293</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154021852116</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ASG-20260918154126177293</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154023364623</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ASG-20260918154126177293</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154024342195</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ASG-20260918154126177293</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918154022601290</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Talent360i_Output.xlsx
+++ b/Talent360i_Output.xlsx
@@ -3816,7 +3816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4403,6 +4403,96 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>2026-09-18T15:39:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REQ-20260918195804693255</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SYN-U031</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Associate Revenue Controller</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Requested</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-18T19:58:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>REQ-20260918200042515999</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SYN-U017</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>P2P Senior Associate</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tax / Withholding &amp; Regulatory Basics</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Assigned</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-18T20:00:42</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4898,6 +4988,80 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>2026-09-18T15:39:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AUD-20260918195804693255</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>assessment_request</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>REQ-20260918195804693255</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>SYN-U031</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skill=Invoicing (Standard/Complex), Level=5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-09-18T19:58:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AUD-20260918200042515999</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>assessment_request</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>REQ-20260918200042515999</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>requested</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>SYN-U017</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skill=Tax / Withholding &amp; Regulatory Basics, Level=5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-09-18T20:00:43</t>
         </is>
       </c>
     </row>
@@ -4912,7 +5076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N191"/>
+  <dimension ref="A1:N201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16794,6 +16958,656 @@
       <c r="M191" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>REV-20260918200726762812</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200427929257</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>1</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>REV-20260918200728879604</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200429777983</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>1</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>REV-20260918200730422617</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200424458847</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>REV-20260918200732341078</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200422336284</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>REV-20260918200734247530</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200426383004</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>REV-20260918200736276243</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200427176463</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>REV-20260918200738075741</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200425294369</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>REV-20260918200739966214</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200428944879</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>REV-20260918200741799433</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200421585636</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>REV-20260918200744869089</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200423635576</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Needs Revision</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Rewrite</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Rewrite required</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -16808,7 +17622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA141"/>
+  <dimension ref="A1:AB151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16934,15 +17748,20 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>ready_for_schedule</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>source_question_reference</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ai_confidence</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>schedule_scope</t>
         </is>
@@ -33686,6 +34505,1236 @@
         <is>
           <t>Requires SME approval before scheduling</t>
         </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200421585636</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>P2P Senior Associate</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Tax / Withholding &amp; Regulatory Basics</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>5</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>What is the main purpose of withholding tax?</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>To increase the overall tax rate</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>To ensure tax revenue is collected in advance</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>To reduce tax liability for corporations</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>To provide tax benefits for nonprofit organizations</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>{"skill": "Tax / Withholding &amp; Regulatory Basics", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y142" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200422336284</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>P2P Senior Associate</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Tax / Withholding &amp; Regulatory Basics</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>5</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Which of the following is typically subject to withholding tax?</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Interest income from savings accounts</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Rental income from property</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Wages paid to employees</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Capital gains from stock sales</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>{"skill": "Tax / Withholding &amp; Regulatory Basics", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y143" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200423635576</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>P2P Senior Associate</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Tax / Withholding &amp; Regulatory Basics</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>5</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>What form is used by employees to indicate their tax withholding preferences?</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Form W-2</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Form 1099</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Form W-4</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Form 1040</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>{"skill": "Tax / Withholding &amp; Regulatory Basics", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y144" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200424458847</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>P2P Senior Associate</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Tax / Withholding &amp; Regulatory Basics</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>5</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>What is the maximum percentage of an employee's paycheck that can be withheld for federal income tax?</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>There is no maximum percentage</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>{"skill": "Tax / Withholding &amp; Regulatory Basics", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y145" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200425294369</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>P2P Senior Associate</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Tax / Withholding &amp; Regulatory Basics</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>5</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Which of the following is a common consequence of failing to withhold the correct amount of tax?</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Increased tax refund</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Penalties and interest charges</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Lower tax liability in the following year</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>No significant impact</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>{"skill": "Tax / Withholding &amp; Regulatory Basics", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y146" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200426383004</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>P2P Senior Associate</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Tax / Withholding &amp; Regulatory Basics</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>5</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>What is the primary purpose of the IRS Form 941?</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>To report annual income tax returns</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>To report quarterly payroll taxes</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>To claim tax credits for businesses</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>To notify the IRS of a business closure</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>{"skill": "Tax / Withholding &amp; Regulatory Basics", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y147" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200427176463</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>P2P Senior Associate</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Tax / Withholding &amp; Regulatory Basics</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>5</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Which of the following types of income is generally exempt from withholding tax?</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Wages</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Dividends</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Interest from municipal bonds</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Bonuses</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>{"skill": "Tax / Withholding &amp; Regulatory Basics", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y148" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200427929257</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>P2P Senior Associate</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Tax / Withholding &amp; Regulatory Basics</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>5</v>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>What is a 1099 form used for?</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>To report wages paid to employees</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>To report miscellaneous income not subject to withholding</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>To report tax credits received</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>To report business expenses</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>{"skill": "Tax / Withholding &amp; Regulatory Basics", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y149" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200428944879</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>P2P Senior Associate</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Tax / Withholding &amp; Regulatory Basics</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>5</v>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>In the context of tax withholding, what does the term 'FICA' stand for?</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Federal Income Contribution Act</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Federal Insurance Contributions Act</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Federal Income Compensation Act</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Federal Insurance Collection Act</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>{"skill": "Tax / Withholding &amp; Regulatory Basics", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y150" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200429777983</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>AP</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>P2P Senior Associate</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Tax / Withholding &amp; Regulatory Basics</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>5</v>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Which of the following best describes the relationship between withholding tax and estimated tax payments?</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Withholding tax is always higher than estimated tax payments.</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Withholding tax is a form of estimated tax payment.</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Estimated tax payments are only for self-employed individuals.</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>There is no relationship between the two.</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>{"skill": "Tax / Withholding &amp; Regulatory Basics", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y151" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -33699,7 +35748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34271,6 +36320,110 @@
       <c r="J11" t="inlineStr">
         <is>
           <t>you can do better</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ASG-20260918200839942746</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SYN-U017</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SCH-005</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Created from approved question bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ASG-20260918200849618778</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SYN-U017</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SCH-005</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Created from approved question bank</t>
         </is>
       </c>
     </row>
@@ -34285,7 +36438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34900,6 +37053,126 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ASG-20260918200839942746</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200421585636</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ASG-20260918200839942746</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200424458847</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ASG-20260918200839942746</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200427176463</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ASG-20260918200839942746</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200428944879</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ASG-20260918200839942746</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200429777983</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ASG-20260918200849618778</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200421585636</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ASG-20260918200849618778</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200424458847</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ASG-20260918200849618778</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200427176463</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ASG-20260918200849618778</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200428944879</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ASG-20260918200849618778</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200429777983</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Talent360i_Output.xlsx
+++ b/Talent360i_Output.xlsx
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1943,6 +1943,131 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>2026-09-18T15:42:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ASG-20260921141731284157</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141432431749</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>To request payment for goods or services</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:18:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ASG-20260921141731284157</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141433758506</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>To provide details about each charge</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:18:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ASG-20260921141731284157</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141434704373</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>It helps in identifying the invoice</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:18:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ASG-20260921141731284157</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141435145644</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>To comply with tax regulations</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:18:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ASG-20260921141731284157</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141436066725</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Review the disputed charges and communicate with the customer</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:18:39</t>
         </is>
       </c>
     </row>
@@ -1957,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2542,6 +2667,85 @@
       <c r="R8" t="inlineStr">
         <is>
           <t>you can do better</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RST-20260921141840236633</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ASG-20260921141731284157</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SYN-U031</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SCH-008</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>100</v>
+      </c>
+      <c r="I9" t="n">
+        <v>75</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Application-calculated result awaiting calibration</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>5</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2976,6 +3180,64 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>RST-20260918131857776584</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USA-20260921141905225057</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SYN-U031</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Assessed</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>RST-20260921141840236633</t>
         </is>
       </c>
     </row>
@@ -2990,7 +3252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3061,12 +3323,12 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>cross_functional_recommendation</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>team_id</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>cross_functional_recommendation</t>
         </is>
       </c>
     </row>
@@ -3130,6 +3392,8 @@
           <t>Assign mapped microlearning / scenario lab and reassess</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3191,6 +3455,8 @@
           <t>Assign mapped microlearning / scenario lab and reassess</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3252,6 +3518,8 @@
           <t>Assign mapped microlearning / scenario lab and reassess</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3313,6 +3581,8 @@
           <t>Assign mapped microlearning / scenario lab and reassess</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3374,6 +3644,8 @@
           <t>No action - at target</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3435,11 +3707,79 @@
           <t>Assign mapped microlearning / scenario lab and reassess</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Consider adjacent skill exposure: Attention to Detail (SOX evidence trail / documentation), R2R Close &amp; Journals (US GAAP / IFRS), Reconciliations &amp; Clearing (SOX/IPE balance sheet recs)</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GAP-20260921141905526887</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SYN-U031</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>No gap</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>TRN-0025, TRN-0026</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No action - at target</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Consider adjacent skill exposure: First Time Right (Quality), Order Validation &amp; Billing Setup, Credit Notes / Adjustments</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4442,7 +4782,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Requested</t>
+          <t>Assigned</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -5076,7 +5416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N201"/>
+  <dimension ref="A1:N213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17608,6 +17948,786 @@
       <c r="M201" t="inlineStr">
         <is>
           <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>REV-20260921141635108949</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141435145644</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>REV-20260921141635967495</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141433352731</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>REV-20260921141636905100</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141433758506</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>REV-20260921141637780266</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141434704373</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>REV-20260921141638703814</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141436546664</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="G206" t="n">
+        <v>1</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Reject</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Rejected: not suitable</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>REV-20260921141639598351</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141436066725</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="G207" t="n">
+        <v>1</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>REV-20260921141640349267</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141432881006</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="G208" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>REV-20260921141641283625</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141432431749</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>1</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>REV-20260921141642118370</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141435648279</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>REV-20260921141643030773</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141434191595</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>1</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>REV-20260921141645083345</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141434191595</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>1</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>REV-20260921141646089162</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Q-AI-20260918200423635576</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>BP-005</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>AP_p2p_senior_associate</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>AP_tax_withholding_regulatory_basics</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>1</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Approved for schedule</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -17622,7 +18742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB151"/>
+  <dimension ref="A1:AB161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34849,7 +35969,7 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>Pending SME Review</t>
+          <t>Needs Revision</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
@@ -35734,6 +36854,1236 @@
         </is>
       </c>
       <c r="Y151" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141432431749</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>O2C</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Associate Revenue Controller</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>5</v>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>What is the primary main purpose of an invoice?</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>To request payment for goods or services</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>To provide a receipt for payment made</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>To summarize financial statements</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>To track inventory levels</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>{"skill": "Invoicing (Standard/Complex)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y152" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141432881006</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>O2C</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Associate Revenue Controller</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>5</v>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>What information is typically NOT included on a standard invoice?</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Invoice number</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Customer's payment history</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Due date</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Total amount due</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>{"skill": "Invoicing (Standard/Complex)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y153" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141433352731</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>O2C</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Associate Revenue Controller</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>5</v>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Which of the following is considered a 'due date'?</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>The date the invoice is generated</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>The date payment is received</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>The date payment is expected</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>The date the service was provided</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Easy</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>{"skill": "Invoicing (Standard/Complex)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y154" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141433758506</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>O2C</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Associate Revenue Controller</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>5</v>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>In a complex invoice, what is the purpose of line item descriptions?</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>To summarize total costs</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>To provide details about each charge</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>To list payment methods</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>To show payment history</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>{"skill": "Invoicing (Standard/Complex)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y155" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141434191595</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>O2C</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Associate Revenue Controller</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>5</v>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>What does the term 'net 30' refer to in invoicing?</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Payment is due within 30 days of the invoice date</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>The invoice is due on the 30th of the month</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Discount available if paid within 30 days</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Invoice requires payment in 30 installments</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>{"skill": "Invoicing (Standard/Complex)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y156" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141434704373</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>O2C</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Associate Revenue Controller</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>5</v>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>What is the significance of including a purchase order number on an invoice?</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>It helps in identifying the invoice</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>It tracks inventory</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>It ensures payment is made quicker</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>It verifies the customer's identity</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>{"skill": "Invoicing (Standard/Complex)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y157" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141435145644</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>O2C</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Associate Revenue Controller</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>5</v>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>In a complex invoice, what is the purpose of applying taxes?</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>To increase profit margin</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>To comply with tax regulations</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>To simplify the invoicing process</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>To confuse the customer</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>{"skill": "Invoicing (Standard/Complex)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y158" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141435648279</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>O2C</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Associate Revenue Controller</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>5</v>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>What is a common mistake when issuing invoices that can lead to payment delays?</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Providing clear payment terms</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Incorrect billing addresses</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Including detailed descriptions of services</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Using professional language</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>{"skill": "Invoicing (Standard/Complex)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y159" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141436066725</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>O2C</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Associate Revenue Controller</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>5</v>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>How should a business handle an invoice dispute from a customer?</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Ignore the dispute</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Send a new invoice immediately</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Review the disputed charges and communicate with the customer</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Threaten legal action</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>{"skill": "Invoicing (Standard/Complex)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y160" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141436546664</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Application-created SME wording override</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>O2C</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Associate Revenue Controller</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>O2C_invoicing_standard_complex</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Invoicing (Standard/Complex)</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>5</v>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>AI-generated from role and skill definition</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Multiple Choice - Scenario</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>When creating a recurring invoice, what is a critical factor to consider?</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>The customer's spending habits</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>The frequency of the service or product delivery</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>The total amount due each time</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>The color of the invoice template</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Pending SME Review</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>{"skill": "Invoicing (Standard/Complex)", "level": 5}</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>Requires SME approval before scheduling</t>
+        </is>
+      </c>
+      <c r="Y161" t="b">
         <v>0</v>
       </c>
     </row>
@@ -35748,7 +38098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36422,6 +38772,58 @@
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>Created from approved question bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ASG-20260921141731284157</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Application-created record</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SYN-U031</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>O2C_associate_revenue_controller</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BP-008</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SCH-008</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>Created from approved question bank</t>
         </is>
@@ -36438,7 +38840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:B66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37173,6 +39575,66 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ASG-20260921141731284157</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141432431749</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ASG-20260921141731284157</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141434704373</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ASG-20260921141731284157</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141433758506</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ASG-20260921141731284157</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141436066725</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ASG-20260921141731284157</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Q-AI-20260921141435145644</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
